--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  18.08.2025 a 24.08.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  18.08.2025 a 24.08.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6DD35E7-52F4-4EDA-81FA-2D1875AAECEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7893D86C-2C73-41B2-B2A5-118464C5A4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="18.08" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="108">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -243,6 +243,154 @@
   </si>
   <si>
     <t xml:space="preserve">BRUNO VINICIUS ISAAC COSTA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDILSON GARCIA                               </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia do endosso de cancelamento da apólice 2024/202
+5 através desse e-mail.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO CASALE                               </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:Cópia da apólice congênere c
+om vigência de 2025 a 2026; Endosso de cancelamento emitido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS J BARROS DA CONCEICAO LTDA ME         </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Documento do veículo, Painel com carro ligado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAIR MORAIS                                  </t>
+  </si>
+  <si>
+    <t>falta de vistoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILVANDO DE ARAUJO PAIVA MAGALHAES           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUANA MORENO MARQUES                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RV COMERCIO E SERVICOS LTDA ME               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOACIR RE                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PEDRO JOSE DO NASCIMENTO LTDA ME             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JILMARA ASSIS RODRIGUES ANTONIO              </t>
+  </si>
+  <si>
+    <t>*****FRUSTRADO******* CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: HODOMETRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FELIPE DE ALMEIDA ROBERTO                    </t>
+  </si>
+  <si>
+    <t>FRUSTRADA, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: LATERAL ESQUERDA, PAINEL HODOMETRO, MOTOR, CHASSI E TRASEIRA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIEL SGRIGNOLI                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: PAINEL COM VEÍCULO LIGADO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDRA ROSANGELA BARROS                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JESSYCA CRISTIAN DA SILVA BARROS             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEILA MARCIA COELHO FABRICIO                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANOEL NERI MARTINS DOS SANTOS               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODRIGO AZEVEDO MARCONDES DE OLIVEIRA        </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senho
+r(a) RODRIGO AZEVEDO MARCONDES DE OLIVEIRA, pois este não consta c
+omo condutor na apólice anterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMILA PETROLLI BUENO                        </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: CHASSI (FOTO DO LOCAL INCORRETO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIO ANDRE PITZER PONTES                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNO COSTA SUEDDE FERREIRA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conforme consulta na central de bônus, identificamos que não
+há possibilidade efetuar a transferência de bônus para o(a) senho
+r(a) BRUNO COSTA SUEDDE FERREIRA, pois este não consta como condut
+or na apólice anterior. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA JULIANA KELLI FIRMINO DE ARAUJO        </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Painel com carro ligado, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELMA CRISTINA BISPO PANTAROTTO              </t>
+  </si>
+  <si>
+    <t>FRUSTRADA, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: TODAS AS FOTOS PENDENTES, A VISTORIA FOI INICIADA E NÃO FINALIZADA PELO SEGURADO.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCOS SANTOS SOUZA                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TATIANA LAMARA GOMES DE OLIVEIRA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRICK ROCHA CAMARGO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SANDRA SUELI DA SILVA MENEZES                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEAN CARLOS GOMES DA SILVA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISMAEL AMARAL DE JESUS                       </t>
+  </si>
+  <si>
+    <t>Conforme CBE pela regra de mudança de cobertura
+, de Indenização Integral para Compreensiva, ocorre a redução de 1
+classe de bônus, assim sendo o correto bônus 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CASSIO ZINI                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE AUGUSTO COLARELLI                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido, a atualização junto a Central de Bô
+nus. </t>
   </si>
 </sst>
 </file>
@@ -308,7 +456,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -520,12 +668,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -651,10 +810,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -668,6 +823,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1159,7 +1321,7 @@
       <c r="G5" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="51" t="s">
+      <c r="H5" s="9" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="27">
@@ -1188,7 +1350,7 @@
       <c r="G6" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="52" t="s">
+      <c r="H6" s="22" t="s">
         <v>24</v>
       </c>
       <c r="I6" s="27">
@@ -1217,7 +1379,7 @@
       <c r="G7" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="53" t="s">
+      <c r="H7" s="12" t="s">
         <v>26</v>
       </c>
       <c r="I7" s="27">
@@ -1246,7 +1408,7 @@
       <c r="G8" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="53" t="s">
+      <c r="H8" s="12" t="s">
         <v>26</v>
       </c>
       <c r="I8" s="27">
@@ -1275,7 +1437,7 @@
       <c r="G9" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="54" t="s">
+      <c r="H9" s="15" t="s">
         <v>30</v>
       </c>
       <c r="I9" s="27">
@@ -1333,7 +1495,7 @@
       <c r="G11" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="51" t="s">
+      <c r="H11" s="9" t="s">
         <v>36</v>
       </c>
       <c r="I11" s="27">
@@ -1391,7 +1553,7 @@
       <c r="G13" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="51" t="s">
+      <c r="H13" s="9" t="s">
         <v>39</v>
       </c>
       <c r="I13" s="27">
@@ -1420,7 +1582,7 @@
       <c r="G14" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="51" t="s">
+      <c r="H14" s="9" t="s">
         <v>41</v>
       </c>
       <c r="I14" s="27">
@@ -1533,7 +1695,7 @@
       <c r="F18" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="58" t="s">
+      <c r="G18" s="54" t="s">
         <v>45</v>
       </c>
       <c r="H18" s="8" t="s">
@@ -1559,13 +1721,13 @@
       <c r="E19" s="18">
         <v>3450049614</v>
       </c>
-      <c r="F19" s="56" t="s">
+      <c r="F19" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="G19" s="55" t="s">
+      <c r="G19" s="51" t="s">
         <v>32</v>
       </c>
-      <c r="H19" s="57" t="s">
+      <c r="H19" s="53" t="s">
         <v>33</v>
       </c>
       <c r="I19" s="27">
@@ -1591,7 +1753,7 @@
       <c r="F20" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="G20" s="59" t="s">
+      <c r="G20" s="55" t="s">
         <v>35</v>
       </c>
       <c r="H20" s="8" t="s">
@@ -2268,371 +2430,879 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="27"/>
+      <c r="B2" s="7">
+        <v>45877</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D2" s="25">
+        <v>133808844</v>
+      </c>
+      <c r="E2" s="56">
+        <v>3450047458</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="I2" s="27">
+        <v>45881</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="27"/>
+      <c r="B3" s="7">
+        <v>45881</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D3" s="25">
+        <v>133803315</v>
+      </c>
+      <c r="E3" s="56">
+        <v>3450047007</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="27">
+        <v>45883</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="27"/>
+      <c r="B4" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D4" s="25">
+        <v>133861062</v>
+      </c>
+      <c r="E4" s="56">
+        <v>3450049812</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="27"/>
+      <c r="B5" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D5" s="25">
+        <v>133868104</v>
+      </c>
+      <c r="E5" s="56">
+        <v>3450050065</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="27"/>
+      <c r="B6" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D6" s="25">
+        <v>133875420</v>
+      </c>
+      <c r="E6" s="56">
+        <v>3450050417</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="I6" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="27"/>
+      <c r="B7" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D7" s="25">
+        <v>133877557</v>
+      </c>
+      <c r="E7" s="56">
+        <v>3450050593</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="27"/>
+      <c r="B8" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D8" s="25">
+        <v>133876760</v>
+      </c>
+      <c r="E8" s="56">
+        <v>3450050549</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="I8" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="27"/>
+      <c r="B9" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D9" s="25">
+        <v>133879524</v>
+      </c>
+      <c r="E9" s="56">
+        <v>3450050692</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="I9" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="27"/>
+      <c r="B10" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D10" s="25">
+        <v>133872254</v>
+      </c>
+      <c r="E10" s="56">
+        <v>3450050186</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="27"/>
+      <c r="B11" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D11" s="25">
+        <v>133870244</v>
+      </c>
+      <c r="E11" s="56">
+        <v>3450050109</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="27"/>
+      <c r="B12" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D12" s="25">
+        <v>133880078</v>
+      </c>
+      <c r="E12" s="56">
+        <v>3450050703</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="27"/>
+      <c r="B13" s="7">
+        <v>45882</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D13" s="25">
+        <v>133922650</v>
+      </c>
+      <c r="E13" s="56">
+        <v>3450053410</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="I13" s="27">
+        <v>45882</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="27"/>
+      <c r="B14" s="7">
+        <v>45882</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D14" s="25">
+        <v>133911512</v>
+      </c>
+      <c r="E14" s="56">
+        <v>3450052507</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="57" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="27">
+        <v>45887</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="27"/>
+      <c r="B15" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D15" s="25">
+        <v>133905990</v>
+      </c>
+      <c r="E15" s="56">
+        <v>3450052199</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I15" s="27">
+        <v>45887</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="27"/>
+      <c r="B16" s="7">
+        <v>45882</v>
+      </c>
+      <c r="C16" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D16" s="25">
+        <v>133911050</v>
+      </c>
+      <c r="E16" s="56">
+        <v>3450052474</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="27">
+        <v>45887</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="27"/>
+      <c r="B17" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C17" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D17" s="25">
+        <v>133935279</v>
+      </c>
+      <c r="E17" s="56">
+        <v>3450050384</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="27"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45889</v>
+      </c>
+      <c r="C18" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D18" s="25">
+        <v>133932051</v>
+      </c>
+      <c r="E18" s="56">
+        <v>3450053772</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="I18" s="27">
+        <v>45888</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="27"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45881</v>
+      </c>
+      <c r="C19" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D19" s="25">
+        <v>133946707</v>
+      </c>
+      <c r="E19" s="56">
+        <v>3450051187</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="58" t="s">
+        <v>90</v>
+      </c>
+      <c r="I19" s="27">
+        <v>45881</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="27"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C20" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D20" s="25">
+        <v>133876306</v>
+      </c>
+      <c r="E20" s="56">
+        <v>3450050527</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I20" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="27"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45884</v>
+      </c>
+      <c r="C21" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D21" s="25">
+        <v>133932144</v>
+      </c>
+      <c r="E21" s="56">
+        <v>3450053783</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="58" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" s="27">
+        <v>45888</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="27"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C22" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D22" s="25">
+        <v>133869524</v>
+      </c>
+      <c r="E22" s="56">
+        <v>3450050087</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22" s="58" t="s">
+        <v>95</v>
+      </c>
+      <c r="I22" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="27"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C23" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D23" s="25">
+        <v>133867026</v>
+      </c>
+      <c r="E23" s="56">
+        <v>3450049944</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" s="58" t="s">
+        <v>97</v>
+      </c>
+      <c r="I23" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="27"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C24" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D24" s="25">
+        <v>133867535</v>
+      </c>
+      <c r="E24" s="56">
+        <v>3450050000</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I24" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="27"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C25" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D25" s="25">
+        <v>133873348</v>
+      </c>
+      <c r="E25" s="56">
+        <v>3450050285</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I25" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="27"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C26" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D26" s="25">
+        <v>133874234</v>
+      </c>
+      <c r="E26" s="56">
+        <v>3450050329</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="I26" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="27"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C27" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D27" s="25">
+        <v>133876009</v>
+      </c>
+      <c r="E27" s="56">
+        <v>3450050505</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I27" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="27"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45882</v>
+      </c>
+      <c r="C28" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D28" s="25">
+        <v>133911850</v>
+      </c>
+      <c r="E28" s="56">
+        <v>3450052573</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H28" s="58" t="s">
+        <v>36</v>
+      </c>
+      <c r="I28" s="27">
+        <v>45882</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="27"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45875</v>
+      </c>
+      <c r="C29" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D29" s="25">
+        <v>133800340</v>
+      </c>
+      <c r="E29" s="56">
+        <v>3450046842</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" s="58" t="s">
+        <v>104</v>
+      </c>
+      <c r="I29" s="27">
+        <v>45883</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="27"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45899</v>
+      </c>
+      <c r="C30" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D30" s="25">
+        <v>133915274</v>
+      </c>
+      <c r="E30" s="56">
+        <v>3450052903</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I30" s="27">
+        <v>45899</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="27"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45875</v>
+      </c>
+      <c r="C31" s="28">
+        <v>45888</v>
+      </c>
+      <c r="D31" s="25">
+        <v>133771620</v>
+      </c>
+      <c r="E31" s="56">
+        <v>3450045126</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" s="58" t="s">
+        <v>107</v>
+      </c>
+      <c r="I31" s="27">
+        <v>45876</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
       <c r="C32" s="28"/>
-      <c r="D32" s="25"/>
+      <c r="D32" s="49"/>
       <c r="E32" s="18"/>
-      <c r="F32" s="12"/>
+      <c r="F32" s="36"/>
       <c r="G32" s="20"/>
       <c r="H32" s="9"/>
       <c r="I32" s="27"/>
@@ -2892,7 +3562,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  18.08.2025 a 24.08.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  18.08.2025 a 24.08.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7893D86C-2C73-41B2-B2A5-118464C5A4B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04633EDB-DDF9-4D08-B682-98DB3912625B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="18.08" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="152">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -391,6 +391,146 @@
 coma liberação do bloqueio será necessário a apresentação do en
 dosso de cancelamento emitido, a atualização junto a Central de Bô
 nus. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MELISSA JARDIM DE SOUZA                      </t>
+  </si>
+  <si>
+    <t>C
+onforme CBE pela regra de mudança de cobertura ocorre a redução de
+uma classes de bônus, assim sendo o correto bônus 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIEGO SANTOS SILVA                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VITORIA DOURADO MARTINS                      </t>
+  </si>
+  <si>
+    <t>RECUSA: SEGURADO NÃO CORRIGIU AS FOTOS Fotos que tiveram repique: Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHRISTIANE KELLY SANTOS DA CUNHA MENDES      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Chassi </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAQUELINE DE SOUSA NASCIMENTO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNO LOPES DE OLIVEIRA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FABIANA DE AZEVEDO PIRES FERREIRA            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRIAN ROMAGNOLI EUPHRASIO                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIO CELSO MACEDO                           </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Frente e lateral do passageiro. Frente e lateral do motorista. Traseira e lateral do motorista. Traseira e lateral do passageiro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALDECY CARDOSO MOREIRA                      </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: DPCUMENTO DO VEICULO. FRENTE E LATERAL DO PASSAGEIRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NADIR CAPPELLETTO JUNIOR                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALESSANDRA NEVES MARTINS                     </t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 19.08.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 189 156 WELLINGTON MENDES RODRIGUES ME    </t>
+  </si>
+  <si>
+    <t>Duplicidade;</t>
+  </si>
+  <si>
+    <t>O veiculo desta proposta se encontra coberto pela apólice 51772025
+51311592788 com vigência até 2026. Para seguirmos com a emissão de
+sta proposta pedimos providenciar o cancelamento da apólice ativa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPRESSO COMERCIO DE BEBIDAS LTDA EPP        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identificamos uma divergência entre o modelo do
+veículo informado na transmissão da proposta. Para garantir a cor
+reçãoe a emissão do seguro com os dados precisos, solicitamos que
+nos encaminhe uma cópia do CRLV </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEVERINO ALBERTO DOS SANTOS FILHO            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIOVANE ROMAO OLMEDO POZZEBON                </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Painel com a motocicleta ligada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRISCILLA RAQUEL DE QUEIROZ P SANTOS ME      </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Chassi Justificativa de Dados Divergentes: CRLV em nome de terceiros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBIRATAN DE JESUS DOS SANTOS                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE TERTULIANO SANTOS VALE MELO             </t>
+  </si>
+  <si>
+    <t>SAO SEBASTIAO LOCACAO DE VEICULOS E TURISMO L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREW LUIS MENDES FERREIRA LTDA EPP         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALETE LENZ                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA PAULA DE SOUZA COSTA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favor enviar cópia completa d
+a apólice anterior 2024/2025 ou CI atual </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVANALDO VIEIRA DOS ANJOS                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SONIA MARIA BARROS SANTOS                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JESSICA CARRARO DE CARLI                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS CARLOS TREVISAN                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARY PINTO                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OZEIAS DOS SANTOS ARTEFATOS DE CIMENTO ME    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEONARDO CRISTIANO DA SILVA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVETE MARLI BELLINI ZARA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JULIANA MARCIA BATISTA DE SA E SOUSA         </t>
   </si>
 </sst>
 </file>
@@ -684,7 +824,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -827,6 +967,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -2709,7 +2858,7 @@
       <c r="G11" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="58" t="s">
+      <c r="H11" s="9" t="s">
         <v>78</v>
       </c>
       <c r="I11" s="27">
@@ -2738,7 +2887,7 @@
       <c r="G12" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="58" t="s">
+      <c r="H12" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I12" s="27">
@@ -2767,7 +2916,7 @@
       <c r="G13" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="58" t="s">
+      <c r="H13" s="9" t="s">
         <v>82</v>
       </c>
       <c r="I13" s="27">
@@ -2883,7 +3032,7 @@
       <c r="G17" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="58" t="s">
+      <c r="H17" s="9" t="s">
         <v>36</v>
       </c>
       <c r="I17" s="27">
@@ -2912,7 +3061,7 @@
       <c r="G18" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="58" t="s">
+      <c r="H18" s="9" t="s">
         <v>88</v>
       </c>
       <c r="I18" s="27">
@@ -2941,7 +3090,7 @@
       <c r="G19" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="H19" s="58" t="s">
+      <c r="H19" s="9" t="s">
         <v>90</v>
       </c>
       <c r="I19" s="27">
@@ -2999,7 +3148,7 @@
       <c r="G21" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="H21" s="58" t="s">
+      <c r="H21" s="9" t="s">
         <v>93</v>
       </c>
       <c r="I21" s="27">
@@ -3028,7 +3177,7 @@
       <c r="G22" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="H22" s="58" t="s">
+      <c r="H22" s="9" t="s">
         <v>95</v>
       </c>
       <c r="I22" s="27">
@@ -3057,7 +3206,7 @@
       <c r="G23" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="H23" s="58" t="s">
+      <c r="H23" s="9" t="s">
         <v>97</v>
       </c>
       <c r="I23" s="27">
@@ -3202,7 +3351,7 @@
       <c r="G28" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="H28" s="58" t="s">
+      <c r="H28" s="9" t="s">
         <v>36</v>
       </c>
       <c r="I28" s="27">
@@ -3231,7 +3380,7 @@
       <c r="G29" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="H29" s="58" t="s">
+      <c r="H29" s="9" t="s">
         <v>104</v>
       </c>
       <c r="I29" s="27">
@@ -3289,7 +3438,7 @@
       <c r="G31" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="H31" s="58" t="s">
+      <c r="H31" s="9" t="s">
         <v>107</v>
       </c>
       <c r="I31" s="27">
@@ -3580,7 +3729,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BD26F43-5C8A-4C67-93F6-3B4E17ED8491}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="15.85546875" style="17" customWidth="1"/>
@@ -3597,7 +3746,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="59" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -3626,393 +3775,971 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="60">
+        <v>45895</v>
+      </c>
+      <c r="C2" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D2" s="25">
+        <v>133826900</v>
+      </c>
+      <c r="E2" s="18">
+        <v>3450048360</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="I2" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="12"/>
+      <c r="B3" s="60">
+        <v>45881</v>
+      </c>
+      <c r="C3" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D3" s="25">
+        <v>133900643</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450052012</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G3" s="58" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="27">
+        <v>45881</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="12"/>
+      <c r="B4" s="60">
+        <v>45881</v>
+      </c>
+      <c r="C4" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D4" s="25">
+        <v>133899667</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450051935</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="I4" s="27">
+        <v>45881</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="15"/>
+      <c r="B5" s="60">
+        <v>45881</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D5" s="25">
+        <v>133886492</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450050990</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I5" s="27">
+        <v>45881</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="9"/>
+      <c r="B6" s="60">
+        <v>45881</v>
+      </c>
+      <c r="C6" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D6" s="25">
+        <v>133883689</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450050770</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I6" s="27">
+        <v>45881</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="9"/>
+      <c r="B7" s="60">
+        <v>45881</v>
+      </c>
+      <c r="C7" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D7" s="25">
+        <v>133888951</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450051198</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G7" s="57" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="27">
+        <v>45881</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="9"/>
+      <c r="B8" s="60">
+        <v>45881</v>
+      </c>
+      <c r="C8" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D8" s="25">
+        <v>133900517</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450052001</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="27">
+        <v>45881</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="9"/>
+      <c r="B9" s="60">
+        <v>45882</v>
+      </c>
+      <c r="C9" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D9" s="25">
+        <v>133905982</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450052188</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="27">
+        <v>45887</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="9"/>
+      <c r="B10" s="60">
+        <v>45883</v>
+      </c>
+      <c r="C10" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D10" s="25">
+        <v>133935397</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450053992</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="I10" s="27">
+        <v>45883</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="29"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
+      <c r="B11" s="60">
+        <v>45883</v>
+      </c>
+      <c r="C11" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D11" s="25">
+        <v>133955878</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450054696</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="I11" s="27">
+        <v>45883</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="9"/>
+      <c r="B12" s="60">
+        <v>45881</v>
+      </c>
+      <c r="C12" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D12" s="25">
+        <v>133831480</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450048580</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I12" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
+      <c r="B13" s="60">
+        <v>45891</v>
+      </c>
+      <c r="C13" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D13" s="25">
+        <v>133991674</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450057182</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I13" s="27">
+        <v>45888</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
+      <c r="B14" s="60">
+        <v>45885</v>
+      </c>
+      <c r="C14" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D14" s="25">
+        <v>133825672</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450048294</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="I14" s="27">
+        <v>45882</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
+      <c r="B15" s="7">
+        <v>45876</v>
+      </c>
+      <c r="C15" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D15" s="25">
+        <v>133821785</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450048030</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="I15" s="27">
+        <v>45880</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="29"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="29"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="29"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="9"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="9"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="9"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="24"/>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="9"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="9"/>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="B16" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C16" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D16" s="25">
+        <v>133891318</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450049889</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="G16" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I16" s="27">
+        <v>45888</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45881</v>
+      </c>
+      <c r="C17" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D17" s="25">
+        <v>133886466</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450050989</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="I17" s="27">
+        <v>45881</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45881</v>
+      </c>
+      <c r="C18" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D18" s="25">
+        <v>133884071</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450050813</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="61" t="s">
+        <v>135</v>
+      </c>
+      <c r="I18" s="27">
+        <v>45881</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45881</v>
+      </c>
+      <c r="C19" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D19" s="25">
+        <v>133882691</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450050758</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I19" s="27">
+        <v>45881</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45881</v>
+      </c>
+      <c r="C20" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D20" s="25">
+        <v>133884174</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450050846</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I20" s="27">
+        <v>45881</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45881</v>
+      </c>
+      <c r="C21" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D21" s="25">
+        <v>133884764</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450050912</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I21" s="27">
+        <v>45881</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45881</v>
+      </c>
+      <c r="C22" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D22" s="25">
+        <v>133885292</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450050934</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I22" s="27">
+        <v>45881</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45881</v>
+      </c>
+      <c r="C23" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D23" s="25">
+        <v>133886200</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450050956</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I23" s="27">
+        <v>45881</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45881</v>
+      </c>
+      <c r="C24" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D24" s="25">
+        <v>133887225</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450051044</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="61" t="s">
+        <v>142</v>
+      </c>
+      <c r="I24" s="27">
+        <v>45883</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45881</v>
+      </c>
+      <c r="C25" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D25" s="25">
+        <v>133888000</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3450051100</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I25" s="27">
+        <v>45881</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45881</v>
+      </c>
+      <c r="C26" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D26" s="25">
+        <v>133889763</v>
+      </c>
+      <c r="E26" s="18">
+        <v>3450051330</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26" s="27">
+        <v>45881</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45881</v>
+      </c>
+      <c r="C27" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D27" s="25">
+        <v>133891148</v>
+      </c>
+      <c r="E27" s="18">
+        <v>3450051407</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G27" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I27" s="27">
+        <v>45881</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45881</v>
+      </c>
+      <c r="C28" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D28" s="25">
+        <v>133893013</v>
+      </c>
+      <c r="E28" s="18">
+        <v>3450051473</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="G28" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I28" s="27">
+        <v>45881</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45881</v>
+      </c>
+      <c r="C29" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D29" s="25">
+        <v>133895953</v>
+      </c>
+      <c r="E29" s="18">
+        <v>3450051715</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="G29" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I29" s="27">
+        <v>45881</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>45881</v>
+      </c>
+      <c r="C30" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D30" s="25">
+        <v>133899379</v>
+      </c>
+      <c r="E30" s="18">
+        <v>3450051902</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="G30" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I30" s="27">
+        <v>45881</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>45881</v>
+      </c>
+      <c r="C31" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D31" s="25">
+        <v>133900805</v>
+      </c>
+      <c r="E31" s="18">
+        <v>3450052023</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="G31" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I31" s="27">
+        <v>45881</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>45877</v>
+      </c>
+      <c r="C32" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D32" s="25">
+        <v>133842513</v>
+      </c>
+      <c r="E32" s="18">
+        <v>3450049009</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="G32" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="H32" s="61" t="s">
+        <v>46</v>
+      </c>
+      <c r="I32" s="27">
+        <v>45882</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>45912</v>
+      </c>
+      <c r="C33" s="28">
+        <v>45889</v>
+      </c>
+      <c r="D33" s="25">
+        <v>133921749</v>
+      </c>
+      <c r="E33" s="18">
+        <v>3450053332</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="G33" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="I33" s="27">
+        <v>45887</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
       <c r="C34" s="28"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="12"/>
+      <c r="D34" s="49"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="36"/>
       <c r="G34" s="24"/>
       <c r="H34" s="9"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:9">
       <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="24"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="6"/>
       <c r="H35" s="9"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:9">
       <c r="A36" s="6"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="24"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="6"/>
       <c r="H36" s="9"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="8"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="15"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="9"/>
       <c r="G37" s="6"/>
       <c r="H37" s="9"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="8"/>
       <c r="C38" s="7"/>
@@ -4022,7 +4749,7 @@
       <c r="G38" s="6"/>
       <c r="H38" s="9"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="8"/>
       <c r="C39" s="7"/>
@@ -4032,7 +4759,7 @@
       <c r="G39" s="6"/>
       <c r="H39" s="9"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="8"/>
       <c r="C40" s="7"/>
@@ -4042,7 +4769,7 @@
       <c r="G40" s="6"/>
       <c r="H40" s="9"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="8"/>
       <c r="C41" s="7"/>
@@ -4052,40 +4779,20 @@
       <c r="G41" s="6"/>
       <c r="H41" s="9"/>
     </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-    </row>
-    <row r="43" spans="1:8">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A17:A36" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A34" xr:uid="{F535CD1B-7EC8-4CD4-9DE2-4943F25AAD12}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G36" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G34" xr:uid="{9AF2051F-77D3-4586-8B0A-6A9380E3F6D6}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:B16" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:B14 A15:A33" xr:uid="{E44F5A38-408F-4061-943F-128F4E144D8E}">
       <formula1>$J$2</formula1>
     </dataValidation>
   </dataValidations>
@@ -6693,6 +7400,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
   <Receiver>
@@ -6742,59 +7458,7 @@
 </spe:Receivers>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-494892</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-494892</Url>
-      <Description>QAFFA7D2F2TC-2102087286-494892</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf1b9912853fe4a934dbc2373304754">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d8d96f03b10d24171ef462918d18284e" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7166,18 +7830,61 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-494892</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-494892</Url>
+      <Description>QAFFA7D2F2TC-2102087286-494892</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098F1F3C-7054-44DA-97C1-1FA0AD811FFC}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098F1F3C-7054-44DA-97C1-1FA0AD811FFC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>